--- a/artfynd/A 15453-2021 artfynd.xlsx
+++ b/artfynd/A 15453-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15453-2021 artfynd.xlsx
+++ b/artfynd/A 15453-2021 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>113630183</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>113630184</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>113630185</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>113630182</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 15453-2021 artfynd.xlsx
+++ b/artfynd/A 15453-2021 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>113630183</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>113630184</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>113630185</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>113630182</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
